--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.15-16-18-identity-access-management/WKBK/90_workbooks/ISMS-IMP-A.5.15-16-18.S3_Access_Review_Results_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.15-16-18-identity-access-management/WKBK/90_workbooks/ISMS-IMP-A.5.15-16-18.S3_Access_Review_Results_20260208.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08.02.2026 11:48</t>
+          <t>08.02.2026 12:25</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Iris Sup</t>
+          <t>David Chief</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="I6" s="8" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Grace Owner</t>
+          <t>Carol Lead</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>System Owner</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="I7" s="8" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Iris Sup</t>
+          <t>Carol Lead</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="I8" s="8" t="n">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Henry Mgr</t>
+          <t>Grace Owner</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>System Owner</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="I9" s="8" t="n">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Emma Head</t>
+          <t>Frank VP</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Security Manager</t>
+          <t>VP Operations</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="I10" s="8" t="n">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Emma Head</t>
+          <t>Henry Mgr</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Security Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="I11" s="8" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Frank VP</t>
+          <t>Emma Head</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>VP Operations</t>
+          <t>Security Manager</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="I12" s="8" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Alice Manager</t>
+          <t>David Chief</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="I13" s="8" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>David Chief</t>
+          <t>Jack Admin</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>IT Administrator</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="I14" s="8" t="n">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Carol Lead</t>
+          <t>Bob Director</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Sales Director</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="I15" s="8" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Emma Head</t>
+          <t>Jack Admin</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Security Manager</t>
+          <t>IT Administrator</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="I16" s="8" t="n">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Frank VP</t>
+          <t>Bob Director</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>VP Operations</t>
+          <t>Sales Director</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="I17" s="8" t="n">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Henry Mgr</t>
+          <t>Grace Owner</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>System Owner</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="I18" s="8" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Alice Manager</t>
+          <t>David Chief</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="I19" s="8" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Bob Director</t>
+          <t>Jack Admin</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Sales Director</t>
+          <t>IT Administrator</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="I20" s="8" t="n">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Frank VP</t>
+          <t>Emma Head</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>VP Operations</t>
+          <t>Security Manager</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="I21" s="8" t="n">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Iris Sup</t>
+          <t>David Chief</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>07.02.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Grace Owner</t>
+          <t>Carol Lead</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -2129,19 +2129,15 @@
           <t>31.12.2026</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>04.02.2026</t>
-        </is>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr"/>
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2159,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Iris Sup</t>
+          <t>Carol Lead</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -2201,7 +2197,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Henry Mgr</t>
+          <t>Grace Owner</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -2209,15 +2205,19 @@
           <t>31.12.2026</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
       <c r="G8" s="8" t="inlineStr"/>
       <c r="H8" s="8" t="inlineStr"/>
       <c r="I8" s="8" t="inlineStr"/>
       <c r="J8" s="8" t="inlineStr"/>
       <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="13" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Emma Head</t>
+          <t>Frank VP</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>07.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Emma Head</t>
+          <t>Henry Mgr</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Frank VP</t>
+          <t>Emma Head</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Alice Manager</t>
+          <t>David Chief</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>05.02.2026</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr"/>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>David Chief</t>
+          <t>Jack Admin</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -2411,19 +2411,15 @@
           <t>31.12.2026</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>05.02.2026</t>
-        </is>
-      </c>
+      <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="8" t="inlineStr"/>
       <c r="J13" s="8" t="inlineStr"/>
       <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2441,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Carol Lead</t>
+          <t>Bob Director</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -2483,7 +2479,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Emma Head</t>
+          <t>Jack Admin</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -2491,19 +2487,15 @@
           <t>31.03.2026</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>05.02.2026</t>
-        </is>
-      </c>
+      <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="8" t="inlineStr"/>
       <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr"/>
       <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2517,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Frank VP</t>
+          <t>Bob Director</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -2533,19 +2525,15 @@
           <t>30.06.2026</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>03.02.2026</t>
-        </is>
-      </c>
+      <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="8" t="inlineStr"/>
       <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="8" t="inlineStr"/>
       <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2555,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Henry Mgr</t>
+          <t>Grace Owner</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -2577,7 +2565,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>02.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr"/>
@@ -2609,7 +2597,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Alice Manager</t>
+          <t>David Chief</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -2617,19 +2605,15 @@
           <t>31.12.2026</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>06.02.2026</t>
-        </is>
-      </c>
+      <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="8" t="inlineStr"/>
       <c r="I18" s="8" t="inlineStr"/>
       <c r="J18" s="8" t="inlineStr"/>
       <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2635,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Bob Director</t>
+          <t>Jack Admin</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -2659,19 +2643,15 @@
           <t>31.12.2026</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>04.02.2026</t>
-        </is>
-      </c>
+      <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
       <c r="I19" s="8" t="inlineStr"/>
       <c r="J19" s="8" t="inlineStr"/>
       <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2673,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Frank VP</t>
+          <t>Emma Head</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2701,15 +2681,19 @@
           <t>31.12.2026</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="inlineStr"/>
       <c r="H20" s="8" t="inlineStr"/>
       <c r="I20" s="8" t="inlineStr"/>
       <c r="J20" s="8" t="inlineStr"/>
       <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="13" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -2829,46 +2813,46 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>REV-0032</t>
+          <t>REV-0045</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>user90</t>
+          <t>user70</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Change Access Level</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>User needs less privilege (Admin → Read/Write)</t>
+          <t>Access not used in 90+ days</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="J6" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
@@ -2884,37 +2868,37 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>REV-0080</t>
+          <t>REV-0003</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>user93</t>
+          <t>user22</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Access not used in 90+ days</t>
+          <t>User promoted (Read → Admin)</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr"/>
@@ -2933,22 +2917,22 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>REV-0038</t>
+          <t>REV-0073</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>user22</t>
+          <t>user59</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2958,7 +2942,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>User left company</t>
+          <t>User no longer needs access</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -2966,11 +2950,17 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>12.01.2026</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -2982,17 +2972,17 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>REV-0048</t>
+          <t>REV-0036</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>user82</t>
+          <t>user52</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -3007,7 +2997,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Temporary project access ended</t>
+          <t>User promoted (Read → Admin)</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -3017,11 +3007,11 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>25.01.2026</t>
+          <t>19.01.2026</t>
         </is>
       </c>
       <c r="J9" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
@@ -3037,17 +3027,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>REV-0051</t>
+          <t>REV-0079</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>user54</t>
+          <t>user48</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -3062,7 +3052,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Access not used in 90+ days</t>
+          <t>User left company</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -3070,17 +3060,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>30.01.2026</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr"/>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3092,17 +3076,17 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>REV-0072</t>
+          <t>REV-0014</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>user58</t>
+          <t>user92</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -3112,24 +3096,30 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Change Access Level</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Temporary project access ended</t>
+          <t>User no longer needs access</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>10.01.2026</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3131,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>REV-0043</t>
+          <t>REV-0052</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3151,7 +3141,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>user8</t>
+          <t>user80</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -3161,30 +3151,24 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Change Access Level</t>
+          <t>Request Justification</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>User promoted (Read → Admin)</t>
+          <t>Missing business justification documentation</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>03.02.2026</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="8" t="inlineStr"/>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3180,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>REV-0002</t>
+          <t>REV-0007</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -3211,7 +3195,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -3231,7 +3215,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>30.01.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="J13" s="8" t="n">
@@ -3251,22 +3235,22 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>REV-0028</t>
+          <t>REV-0073</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>user8</t>
+          <t>user68</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -3286,11 +3270,11 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>07.02.2026</t>
+          <t>31.01.2026</t>
         </is>
       </c>
       <c r="J14" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
@@ -3306,42 +3290,42 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>REV-0035</t>
+          <t>REV-0070</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>user58</t>
+          <t>user21</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>Temporary project access ended</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>25.01.2026</t>
+          <t>23.01.2026</t>
         </is>
       </c>
       <c r="J15" s="8" t="n">
@@ -3361,12 +3345,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>REV-0040</t>
+          <t>REV-0035</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -3376,35 +3360,29 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Request Justification</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>User left company</t>
+          <t>Missing business justification documentation</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>13.01.2026</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr"/>
+      <c r="J16" s="8" t="inlineStr"/>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3416,32 +3394,32 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>REV-0023</t>
+          <t>REV-0038</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>File Server</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>user42</t>
+          <t>user47</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Request Justification</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Access appropriate for user role</t>
+          <t>Missing business justification documentation</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -3451,11 +3429,11 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>30.01.2026</t>
+          <t>29.01.2026</t>
         </is>
       </c>
       <c r="J17" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
@@ -3471,7 +3449,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>REV-0022</t>
+          <t>REV-0055</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -3481,7 +3459,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>user28</t>
+          <t>user34</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -3491,26 +3469,26 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Access appropriate for user role</t>
+          <t>User no longer needs access</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>12.01.2026</t>
         </is>
       </c>
       <c r="J18" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
@@ -3526,17 +3504,17 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>REV-0036</t>
+          <t>REV-0027</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>user13</t>
+          <t>user96</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -3546,26 +3524,26 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>User changed departments</t>
+          <t>Temporary project access ended</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>23.01.2026</t>
         </is>
       </c>
       <c r="J19" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
@@ -3581,50 +3559,44 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>REV-0069</t>
+          <t>REV-0022</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>user65</t>
+          <t>user96</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Request Justification</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>User changed departments</t>
+          <t>Missing business justification documentation</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr"/>
+      <c r="J20" s="8" t="inlineStr"/>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3608,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>REV-0038</t>
+          <t>REV-0023</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3646,7 +3618,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>user30</t>
+          <t>user78</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -3656,17 +3628,17 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>Access not used in 90+ days</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr"/>
@@ -3685,50 +3657,44 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>REV-0030</t>
+          <t>REV-0062</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>user40</t>
+          <t>user55</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Request Justification</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>User left company</t>
+          <t>Missing business justification documentation</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>06.02.2026</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr"/>
+      <c r="J22" s="8" t="inlineStr"/>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3740,17 +3706,17 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>REV-0023</t>
+          <t>REV-0042</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>user73</t>
+          <t>user36</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -3765,7 +3731,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>User no longer needs access</t>
+          <t>User left company</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -3773,17 +3739,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>06.02.2026</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3795,44 +3755,50 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>REV-0079</t>
+          <t>REV-0017</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>user42</t>
+          <t>user56</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>User needs less privilege (Admin → Read/Write)</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr"/>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>26.01.2026</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -3844,44 +3810,50 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>REV-0027</t>
+          <t>REV-0034</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>user74</t>
+          <t>user24</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Request Justification</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>User no longer needs access</t>
+          <t>Missing business justification documentation</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr"/>
-      <c r="J25" s="8" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>27.01.2026</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -3893,50 +3865,44 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>REV-0016</t>
+          <t>REV-0079</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>user65</t>
+          <t>user67</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>User changed departments</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>06.02.2026</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr"/>
+      <c r="J26" s="8" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3948,46 +3914,46 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>REV-0071</t>
+          <t>REV-0032</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>File Server</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>user2</t>
+          <t>user19</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Access appropriate for user role</t>
+          <t>Temporary project access ended</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>05.02.2026</t>
+          <t>28.01.2026</t>
         </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
@@ -4003,17 +3969,17 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>REV-0047</t>
+          <t>REV-0045</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>user3</t>
+          <t>user57</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -4023,26 +3989,26 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Change Access Level</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>User needs less privilege (Admin → Read/Write)</t>
+          <t>Access appropriate for user role</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>05.02.2026</t>
+          <t>06.02.2026</t>
         </is>
       </c>
       <c r="J28" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
@@ -4058,7 +4024,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>REV-0003</t>
+          <t>REV-0030</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -4068,7 +4034,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>user24</t>
+          <t>user29</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -4078,26 +4044,26 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>User no longer needs access</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>29.01.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
@@ -4113,22 +4079,22 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>REV-0064</t>
+          <t>REV-0070</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>user22</t>
+          <t>user55</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -4148,11 +4114,11 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>08.02.2026</t>
+          <t>29.01.2026</t>
         </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
@@ -4168,17 +4134,17 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>REV-0059</t>
+          <t>REV-0007</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>user67</t>
+          <t>user26</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -4188,12 +4154,12 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>Access appropriate for user role</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -4201,11 +4167,17 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr"/>
-      <c r="J31" s="8" t="inlineStr"/>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>06.02.2026</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4189,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>REV-0008</t>
+          <t>REV-0044</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -4227,7 +4199,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>user49</t>
+          <t>user99</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -4237,12 +4209,12 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>Access appropriate for user role</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -4250,11 +4222,17 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr"/>
-      <c r="J32" s="8" t="inlineStr"/>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4266,22 +4244,22 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>REV-0004</t>
+          <t>REV-0058</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>File Server</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>user56</t>
+          <t>user15</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -4301,11 +4279,11 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>02.02.2026</t>
         </is>
       </c>
       <c r="J33" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
@@ -4321,7 +4299,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>REV-0061</t>
+          <t>REV-0011</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -4331,27 +4309,27 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>user82</t>
+          <t>user30</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>Access not used in 90+ days</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr"/>
@@ -4370,44 +4348,50 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>REV-0041</t>
+          <t>REV-0045</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>user32</t>
+          <t>user21</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Change Access Level</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Temporary project access ended</t>
+          <t>Access appropriate for user role</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="inlineStr"/>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4419,46 +4403,46 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>REV-0042</t>
+          <t>REV-0047</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>user5</t>
+          <t>user31</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Change Access Level</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>User needs less privilege (Admin → Read/Write)</t>
+          <t>Access appropriate for user role</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>23.01.2026</t>
+          <t>31.01.2026</t>
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
@@ -4474,46 +4458,46 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>REV-0018</t>
+          <t>REV-0029</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>user31</t>
+          <t>user85</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>User no longer needs access</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>28.01.2026</t>
+          <t>30.01.2026</t>
         </is>
       </c>
       <c r="J37" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
@@ -4529,22 +4513,22 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>REV-0068</t>
+          <t>REV-0071</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>user17</t>
+          <t>user31</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -4564,11 +4548,11 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>02.02.2026</t>
+          <t>29.01.2026</t>
         </is>
       </c>
       <c r="J38" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
@@ -4584,17 +4568,17 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>REV-0063</t>
+          <t>REV-0026</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>user8</t>
+          <t>user18</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -4604,24 +4588,30 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>Access not used in 90+ days</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="inlineStr"/>
-      <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4633,50 +4623,44 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>REV-0059</t>
+          <t>REV-0051</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>user36</t>
+          <t>user88</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Change Access Level</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Temporary project access ended</t>
+          <t>User changed departments</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>22.01.2026</t>
-        </is>
-      </c>
-      <c r="J40" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K40" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr"/>
+      <c r="J40" s="8" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4672,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>REV-0058</t>
+          <t>REV-0017</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>user13</t>
+          <t>user92</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -4708,24 +4692,30 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Change Access Level</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Temporary project access ended</t>
+          <t>User left company</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="inlineStr"/>
-      <c r="J41" s="8" t="inlineStr"/>
-      <c r="K41" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>29.01.2026</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4727,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>REV-0066</t>
+          <t>REV-0036</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -4757,26 +4747,26 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>User no longer needs access</t>
+          <t>Temporary project access ended</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>22.01.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
@@ -4792,22 +4782,22 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>REV-0072</t>
+          <t>REV-0020</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>user47</t>
+          <t>user89</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -4825,17 +4815,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>30.01.2026</t>
-        </is>
-      </c>
-      <c r="J43" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K43" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+      <c r="I43" s="8" t="inlineStr"/>
+      <c r="J43" s="8" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4831,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>REV-0010</t>
+          <t>REV-0053</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>user34</t>
+          <t>user13</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -4882,11 +4866,11 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>31.01.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="J44" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
@@ -4902,50 +4886,44 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>REV-0007</t>
+          <t>REV-0040</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>user48</t>
+          <t>user35</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>Access appropriate for user role</t>
+          <t>Access not used in 90+ days</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>29.01.2026</t>
-        </is>
-      </c>
-      <c r="J45" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K45" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr"/>
+      <c r="J45" s="8" t="inlineStr"/>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -4957,44 +4935,50 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>REV-0029</t>
+          <t>REV-0072</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>File Server</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>user35</t>
+          <t>user40</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>User left company</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr"/>
-      <c r="J46" s="8" t="inlineStr"/>
-      <c r="K46" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>12.01.2026</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5006,7 +4990,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>REV-0058</t>
+          <t>REV-0017</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -5016,12 +5000,12 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>user27</t>
+          <t>user30</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -5041,7 +5025,7 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>31.01.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="J47" s="8" t="n">
@@ -5061,46 +5045,46 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>REV-0004</t>
+          <t>REV-0030</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>user100</t>
+          <t>user72</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>User no longer needs access</t>
+          <t>Temporary project access ended</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>18.01.2026</t>
+          <t>24.01.2026</t>
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
@@ -5116,50 +5100,44 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>REV-0058</t>
+          <t>REV-0026</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>user37</t>
+          <t>user82</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Request Justification</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>User no longer needs access</t>
+          <t>Missing business justification documentation</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>27.01.2026</t>
-        </is>
-      </c>
-      <c r="J49" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K49" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr"/>
+      <c r="J49" s="8" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -5171,17 +5149,17 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>REV-0074</t>
+          <t>REV-0038</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>user50</t>
+          <t>user91</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -5206,11 +5184,11 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>08.02.2026</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="J50" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
@@ -5226,46 +5204,46 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>REV-0015</t>
+          <t>REV-0027</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>user64</t>
+          <t>user53</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>User changed departments</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>30.01.2026</t>
+          <t>24.01.2026</t>
         </is>
       </c>
       <c r="J51" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
@@ -5281,7 +5259,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>REV-0059</t>
+          <t>REV-0056</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -5291,34 +5269,40 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>user73</t>
+          <t>user8</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Access not used in 90+ days</t>
+          <t>Temporary project access ended</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="inlineStr"/>
-      <c r="J52" s="8" t="inlineStr"/>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>22.01.2026</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5330,17 +5314,17 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>REV-0012</t>
+          <t>REV-0072</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>user11</t>
+          <t>user76</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -5350,26 +5334,26 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>Access appropriate for user role</t>
+          <t>User changed departments</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>29.01.2026</t>
+          <t>23.01.2026</t>
         </is>
       </c>
       <c r="J53" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
@@ -5385,32 +5369,32 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>REV-0067</t>
+          <t>REV-0038</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>user50</t>
+          <t>user75</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Request Justification</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>Access appropriate for user role</t>
+          <t>Missing business justification documentation</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -5420,11 +5404,11 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>08.02.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="J54" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
@@ -5440,46 +5424,46 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>REV-0061</t>
+          <t>REV-0044</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>File Server</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>user95</t>
+          <t>user31</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>Access not used in 90+ days</t>
+          <t>User promoted (Read → Admin)</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="J55" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
@@ -5495,7 +5479,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>REV-0040</t>
+          <t>REV-0064</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -5505,40 +5489,34 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>user88</t>
+          <t>user37</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Change Access Level</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>User promoted (Read → Admin)</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>25.01.2026</t>
-        </is>
-      </c>
-      <c r="J56" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K56" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr"/>
+      <c r="J56" s="8" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -5550,22 +5528,22 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>REV-0028</t>
+          <t>REV-0016</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>user45</t>
+          <t>user92</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -5575,7 +5553,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>User left company</t>
+          <t>Access not used in 90+ days</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -5585,11 +5563,11 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>31.01.2026</t>
+          <t>16.01.2026</t>
         </is>
       </c>
       <c r="J57" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
@@ -5605,42 +5583,42 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>REV-0032</t>
+          <t>REV-0010</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>user46</t>
+          <t>user58</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>User changed departments</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="J58" s="8" t="n">
@@ -5660,32 +5638,32 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>REV-0008</t>
+          <t>REV-0073</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>user5</t>
+          <t>user50</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>Access appropriate for user role</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -5695,11 +5673,11 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>25.01.2026</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="J59" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
@@ -5715,17 +5693,17 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>REV-0076</t>
+          <t>REV-0004</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>user78</t>
+          <t>user12</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -5735,12 +5713,12 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Request Justification</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Missing business justification documentation</t>
+          <t>Access appropriate for user role</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -5748,11 +5726,17 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr"/>
-      <c r="J60" s="8" t="inlineStr"/>
-      <c r="K60" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>08.02.2026</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5764,37 +5748,37 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>REV-0029</t>
+          <t>REV-0027</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>user75</t>
+          <t>user60</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Request Justification</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>Access not used in 90+ days</t>
+          <t>Missing business justification documentation</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr"/>
@@ -5813,46 +5797,46 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>REV-0009</t>
+          <t>REV-0002</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>user44</t>
+          <t>user46</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>User no longer needs access</t>
+          <t>Access appropriate for user role</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="J62" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
@@ -5868,50 +5852,44 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>REV-0057</t>
+          <t>REV-0002</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>user41</t>
+          <t>user54</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>Access appropriate for user role</t>
+          <t>User changed departments</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>03.02.2026</t>
-        </is>
-      </c>
-      <c r="J63" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr"/>
+      <c r="K63" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -5923,22 +5901,22 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>REV-0020</t>
+          <t>REV-0079</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>user23</t>
+          <t>user80</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -5958,11 +5936,11 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>30.01.2026</t>
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
@@ -5978,7 +5956,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>REV-0074</t>
+          <t>REV-0056</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -5988,7 +5966,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>user43</t>
+          <t>user65</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -5998,26 +5976,26 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>User changed departments</t>
+          <t>Access appropriate for user role</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>31.01.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="J65" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
@@ -6239,21 +6217,21 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -6286,18 +6264,18 @@
         <v>7</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
@@ -6330,18 +6308,18 @@
         <v>6</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
@@ -6371,30 +6349,30 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Needs Improvement</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
@@ -6415,30 +6393,30 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Needs Improvement</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
@@ -6459,28 +6437,28 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
@@ -6503,30 +6481,30 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="8" t="n">
-        <v>5</v>
-      </c>
       <c r="F11" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Needs Improvement</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
@@ -6547,21 +6525,21 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
@@ -6591,13 +6569,13 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -6605,7 +6583,7 @@
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
@@ -6635,30 +6613,30 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Needs Improvement</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
